--- a/app/templates/Template_EquiArena.xlsx
+++ b/app/templates/Template_EquiArena.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FC55B9-D11A-488B-89BA-2A69A2386188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DF63C9-7A68-4BFC-B408-A34A077C948A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,7 +734,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -766,479 +766,473 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="17" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="17" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0" hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2131,388 +2125,388 @@
   <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="19" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="19" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" style="19" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="19" customWidth="1"/>
-    <col min="8" max="10" width="13" style="19" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" style="19" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="19" customWidth="1"/>
-    <col min="13" max="14" width="10.6640625" style="19" customWidth="1"/>
-    <col min="15" max="16384" width="10.33203125" style="19"/>
+    <col min="1" max="1" width="6.88671875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="18" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" style="18" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="18" customWidth="1"/>
+    <col min="8" max="10" width="13" style="18" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" style="18" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" style="18" customWidth="1"/>
+    <col min="13" max="14" width="10.6640625" style="18" customWidth="1"/>
+    <col min="15" max="16384" width="10.33203125" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18"/>
+      <c r="A1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="23"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="23"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="23"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="26"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:13" ht="5.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="M7" s="29"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
+      <c r="M7" s="28"/>
     </row>
     <row r="8" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:13" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
     </row>
     <row r="10" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="131" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32" t="s">
+      <c r="C10" s="131"/>
+      <c r="D10" s="131" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32" t="s">
+      <c r="E10" s="131"/>
+      <c r="F10" s="131" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32" t="s">
+      <c r="G10" s="131"/>
+      <c r="H10" s="131" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
     </row>
     <row r="11" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="131"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
     </row>
     <row r="12" spans="1:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="122" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="123"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
     </row>
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
     </row>
     <row r="15" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52" t="s">
+      <c r="A16" s="41"/>
+      <c r="B16" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="54" t="s">
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="54"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="55" t="s">
+      <c r="G16" s="126"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="J16" s="56"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
-      <c r="B17" s="57" t="s">
+      <c r="A17" s="41"/>
+      <c r="B17" s="132" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="57" t="s">
+      <c r="C17" s="133"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="132" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="59"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="64"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="65"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="107"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="44"/>
     </row>
     <row r="19" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="66"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="67"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="65"/>
-    </row>
-    <row r="20" spans="1:14" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="68"/>
-      <c r="B20" s="69" t="s">
+      <c r="A19" s="45"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="46"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="44"/>
+    </row>
+    <row r="20" spans="1:14" s="48" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="47"/>
+      <c r="B20" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="69"/>
-      <c r="D20" s="70"/>
-      <c r="F20" s="72" t="s">
+      <c r="C20" s="127"/>
+      <c r="D20" s="129"/>
+      <c r="F20" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="67"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="65"/>
-    </row>
-    <row r="21" spans="1:14" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
-      <c r="B21" s="76"/>
-      <c r="C21" s="76"/>
-      <c r="D21" s="77"/>
-      <c r="F21" s="57" t="s">
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="46"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="44"/>
+    </row>
+    <row r="21" spans="1:14" s="48" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="52"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="130"/>
+      <c r="F21" s="132" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="58"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="67"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="65"/>
-    </row>
-    <row r="22" spans="1:14" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="75"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="53"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="67"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="65"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="46"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="44"/>
+    </row>
+    <row r="22" spans="1:14" s="48" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="42"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="46"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="44"/>
     </row>
     <row r="23" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="80"/>
-      <c r="L23" s="134"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="55"/>
+      <c r="L23" s="95"/>
     </row>
     <row r="24" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="81"/>
-      <c r="B24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="135"/>
+      <c r="A24" s="56"/>
+      <c r="B24" s="56"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="96"/>
     </row>
     <row r="25" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="82" t="s">
+      <c r="A25" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="86" t="s">
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="86" t="s">
+      <c r="I25" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="87" t="s">
+      <c r="J25" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="K25" s="88"/>
-      <c r="L25" s="89"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="64"/>
     </row>
     <row r="26" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="91" t="s">
+      <c r="B26" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="94" t="s">
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="69" t="s">
         <v>31</v>
       </c>
       <c r="H26" s="13">
@@ -2526,519 +2520,518 @@
         <f>+H26+0.0045</f>
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="K26" s="95"/>
-      <c r="L26" s="137"/>
-      <c r="N26" s="136"/>
+      <c r="K26" s="70"/>
+      <c r="N26" s="97"/>
     </row>
     <row r="27" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="90" t="s">
+      <c r="A27" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="91" t="s">
+      <c r="B27" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="94" t="s">
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="H27" s="96">
+      <c r="H27" s="71">
         <f>H26+L27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="96">
+      <c r="I27" s="71">
         <f>I26+L27</f>
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="J27" s="96">
+      <c r="J27" s="71">
         <f>J26+L27</f>
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="K27" s="97"/>
-      <c r="L27" s="136"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="97"/>
     </row>
     <row r="28" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="91" t="s">
+      <c r="B28" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="94" t="s">
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="98">
+      <c r="H28" s="73">
         <v>10</v>
       </c>
-      <c r="I28" s="98">
+      <c r="I28" s="73">
         <v>10</v>
       </c>
-      <c r="J28" s="98">
+      <c r="J28" s="73">
         <v>10</v>
       </c>
-      <c r="K28" s="99"/>
-      <c r="L28" s="136"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="97"/>
     </row>
     <row r="29" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="90" t="s">
+      <c r="A29" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="91" t="s">
+      <c r="B29" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="94" t="s">
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="98">
+      <c r="H29" s="73">
         <v>45</v>
       </c>
-      <c r="I29" s="98">
+      <c r="I29" s="73">
         <v>45</v>
       </c>
-      <c r="J29" s="98">
+      <c r="J29" s="73">
         <v>45</v>
       </c>
-      <c r="K29" s="99"/>
-      <c r="L29" s="138"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="95"/>
     </row>
     <row r="30" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="90" t="s">
+      <c r="A30" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="91" t="s">
+      <c r="B30" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="94" t="s">
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="H30" s="96">
+      <c r="H30" s="71">
         <f>H27+N26</f>
         <v>0</v>
       </c>
-      <c r="I30" s="96">
+      <c r="I30" s="71">
         <f>I27+N26</f>
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="J30" s="96">
+      <c r="J30" s="71">
         <f>J27+N26</f>
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="K30" s="99"/>
-      <c r="L30" s="34"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="30"/>
     </row>
     <row r="31" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="91" t="s">
+      <c r="B31" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="94" t="s">
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="96">
+      <c r="H31" s="71">
         <f>IF(H30=0,0,H30+L28)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="96">
+      <c r="I31" s="71">
         <f>IF(I30=0,0,I30+L28)</f>
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="J31" s="96">
+      <c r="J31" s="71">
         <f>IF(J30=0,0,J30+L28)</f>
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="K31" s="99"/>
-      <c r="L31" s="34"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="30"/>
     </row>
     <row r="32" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="90" t="s">
+      <c r="A32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="91" t="s">
+      <c r="B32" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="94" t="s">
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="98">
+      <c r="H32" s="73">
         <v>20</v>
       </c>
-      <c r="I32" s="98">
+      <c r="I32" s="73">
         <v>20</v>
       </c>
-      <c r="J32" s="98">
+      <c r="J32" s="73">
         <v>20</v>
       </c>
-      <c r="K32" s="100"/>
-      <c r="L32" s="34"/>
+      <c r="K32" s="75"/>
+      <c r="L32" s="30"/>
     </row>
     <row r="33" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="90" t="s">
+      <c r="A33" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="101" t="s">
+      <c r="B33" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="102"/>
-      <c r="G33" s="94" t="s">
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="H33" s="103">
+      <c r="H33" s="136">
         <v>11.5</v>
       </c>
-      <c r="I33" s="103">
+      <c r="I33" s="136">
         <v>11.7</v>
       </c>
-      <c r="J33" s="103">
+      <c r="J33" s="136">
         <v>11.8</v>
       </c>
-      <c r="K33" s="104"/>
-      <c r="L33" s="34"/>
+      <c r="K33" s="78"/>
+      <c r="L33" s="30"/>
     </row>
     <row r="34" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="90" t="s">
+      <c r="A34" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="101" t="s">
+      <c r="B34" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="94" t="s">
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="103">
+      <c r="H34" s="136">
         <v>2.9</v>
       </c>
-      <c r="I34" s="103">
+      <c r="I34" s="136">
         <v>2.7</v>
       </c>
-      <c r="J34" s="103">
+      <c r="J34" s="136">
         <v>2.8</v>
       </c>
-      <c r="K34" s="106"/>
-      <c r="L34" s="34"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="30"/>
     </row>
     <row r="35" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="90" t="s">
+      <c r="A35" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="101" t="s">
+      <c r="B35" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="92"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="94" t="s">
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="130">
+      <c r="H35" s="94">
         <f>ROUNDUP((H34/H33*100),0)</f>
         <v>26</v>
       </c>
-      <c r="I35" s="130">
+      <c r="I35" s="94">
         <f t="shared" ref="I35:J35" si="0">ROUNDUP((I34/I33*100),0)</f>
         <v>24</v>
       </c>
-      <c r="J35" s="130">
+      <c r="J35" s="94">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
     </row>
     <row r="36" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="107" t="s">
+      <c r="B36" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="92"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="94" t="s">
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="131">
+      <c r="H36" s="119">
         <f>ROUNDUP((AVERAGE(H35:J35)),0)</f>
         <v>25</v>
       </c>
-      <c r="I36" s="132"/>
-      <c r="J36" s="133"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
+      <c r="I36" s="120"/>
+      <c r="J36" s="121"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
     </row>
     <row r="37" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="108"/>
-      <c r="B37" s="108"/>
-      <c r="C37" s="109"/>
-      <c r="D37" s="110"/>
-      <c r="E37" s="110"/>
-      <c r="F37" s="110"/>
-      <c r="G37" s="110"/>
-      <c r="H37" s="110"/>
-      <c r="I37" s="110"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="85"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="112" t="s">
+      <c r="A38" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="113"/>
-      <c r="C38" s="114"/>
-      <c r="D38" s="112" t="s">
+      <c r="B38" s="116"/>
+      <c r="C38" s="115"/>
+      <c r="D38" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115" t="s">
+      <c r="E38" s="115"/>
+      <c r="F38" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="116"/>
-      <c r="H38" s="116"/>
-      <c r="I38" s="116"/>
-      <c r="J38" s="117"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="87"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="88"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
     </row>
     <row r="39" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="119"/>
-      <c r="C39" s="120"/>
-      <c r="D39" s="118" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="110"/>
+      <c r="D39" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="120"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
+      <c r="E39" s="110"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
     </row>
     <row r="40" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="118" t="s">
+      <c r="A40" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="119"/>
-      <c r="C40" s="120"/>
-      <c r="D40" s="118" t="s">
+      <c r="B40" s="109"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="120"/>
-      <c r="F40" s="121"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
+      <c r="E40" s="110"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="87"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="87"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
     </row>
     <row r="41" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="118" t="s">
+      <c r="A41" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="120"/>
-      <c r="D41" s="118" t="s">
+      <c r="B41" s="109"/>
+      <c r="C41" s="110"/>
+      <c r="D41" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="E41" s="120"/>
-      <c r="F41" s="51"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
+      <c r="E41" s="110"/>
+      <c r="F41" s="41"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
     </row>
     <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="122" t="s">
+      <c r="A42" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="B42" s="123"/>
-      <c r="C42" s="124"/>
-      <c r="D42" s="118" t="s">
+      <c r="B42" s="112"/>
+      <c r="C42" s="113"/>
+      <c r="D42" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="E42" s="120"/>
-      <c r="F42" s="51"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="41"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
     </row>
     <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="122" t="s">
+      <c r="A43" s="111" t="s">
         <v>64</v>
       </c>
-      <c r="B43" s="123"/>
-      <c r="C43" s="124"/>
-      <c r="D43" s="118" t="s">
+      <c r="B43" s="112"/>
+      <c r="C43" s="113"/>
+      <c r="D43" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="120"/>
-      <c r="F43" s="51"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
+      <c r="E43" s="110"/>
+      <c r="F43" s="41"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
     </row>
     <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="118" t="s">
+      <c r="A44" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="119"/>
-      <c r="C44" s="120"/>
-      <c r="D44" s="118" t="s">
+      <c r="B44" s="109"/>
+      <c r="C44" s="110"/>
+      <c r="D44" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="E44" s="120"/>
-      <c r="F44" s="51"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="41"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
     </row>
     <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="118" t="s">
+      <c r="A45" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="119"/>
-      <c r="C45" s="120"/>
-      <c r="D45" s="118" t="s">
+      <c r="B45" s="109"/>
+      <c r="C45" s="110"/>
+      <c r="D45" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="E45" s="120"/>
-      <c r="F45" s="51"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="41"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
     </row>
     <row r="46" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="125"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="111"/>
-      <c r="D46" s="111"/>
-      <c r="E46" s="111"/>
-      <c r="F46" s="111"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="111"/>
-      <c r="J46" s="111"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
+      <c r="A46" s="90"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="85"/>
+      <c r="H46" s="85"/>
+      <c r="I46" s="85"/>
+      <c r="J46" s="85"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
     </row>
     <row r="47" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="126"/>
-      <c r="B47" s="126"/>
-      <c r="C47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
+      <c r="A47" s="91"/>
+      <c r="B47" s="91"/>
+      <c r="C47" s="85"/>
+      <c r="J47" s="85"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
     </row>
     <row r="48" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="126"/>
-      <c r="B48" s="126"/>
-      <c r="C48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
+      <c r="A48" s="91"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="85"/>
+      <c r="J48" s="85"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
     </row>
     <row r="49" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="126"/>
-      <c r="B49" s="126"/>
-      <c r="C49" s="111"/>
-      <c r="J49" s="111"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
+      <c r="A49" s="91"/>
+      <c r="B49" s="91"/>
+      <c r="C49" s="85"/>
+      <c r="J49" s="85"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
     </row>
     <row r="50" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="127"/>
-      <c r="B50" s="127"/>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
-      <c r="E50" s="111"/>
-      <c r="F50" s="111"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="111"/>
-      <c r="J50" s="111"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
+      <c r="A50" s="92"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="85"/>
+      <c r="D50" s="85"/>
+      <c r="E50" s="85"/>
+      <c r="F50" s="85"/>
+      <c r="G50" s="85"/>
+      <c r="H50" s="85"/>
+      <c r="I50" s="85"/>
+      <c r="J50" s="85"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="128" t="s">
+      <c r="A51" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="128"/>
-      <c r="C51" s="111"/>
-      <c r="D51" s="111"/>
-      <c r="E51" s="111"/>
-      <c r="F51" s="111"/>
-      <c r="G51" s="111"/>
-      <c r="H51" s="111"/>
-      <c r="I51" s="111"/>
-      <c r="J51" s="111"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
+      <c r="B51" s="93"/>
+      <c r="C51" s="85"/>
+      <c r="D51" s="85"/>
+      <c r="E51" s="85"/>
+      <c r="F51" s="85"/>
+      <c r="G51" s="85"/>
+      <c r="H51" s="85"/>
+      <c r="I51" s="85"/>
+      <c r="J51" s="85"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
     </row>
     <row r="52" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="128" t="s">
+      <c r="A52" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="B52" s="128"/>
-      <c r="C52" s="111"/>
-      <c r="D52" s="111"/>
-      <c r="E52" s="111"/>
-      <c r="F52" s="97" t="s">
+      <c r="B52" s="93"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="85"/>
+      <c r="F52" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="111"/>
-      <c r="J52" s="111"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
+      <c r="G52" s="85"/>
+      <c r="H52" s="85"/>
+      <c r="I52" s="85"/>
+      <c r="J52" s="85"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
     </row>
     <row r="53" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="129" t="s">
+      <c r="A54" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="129"/>
-      <c r="C54" s="129"/>
-      <c r="D54" s="129"/>
-      <c r="E54" s="129"/>
-      <c r="F54" s="129"/>
-      <c r="G54" s="129"/>
-      <c r="H54" s="129"/>
-      <c r="I54" s="129"/>
-      <c r="J54" s="129"/>
+      <c r="B54" s="98"/>
+      <c r="C54" s="98"/>
+      <c r="D54" s="98"/>
+      <c r="E54" s="98"/>
+      <c r="F54" s="98"/>
+      <c r="G54" s="98"/>
+      <c r="H54" s="98"/>
+      <c r="I54" s="98"/>
+      <c r="J54" s="98"/>
     </row>
     <row r="55" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3050,6 +3043,29 @@
     <protectedRange sqref="H31:J31" name="Rango8_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:G17"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="I16:I18"/>
@@ -3066,29 +3082,6 @@
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3116,10 +3109,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="14"/>
+      <c r="B2" s="135"/>
       <c r="C2" s="5" t="s">
         <v>10</v>
       </c>

--- a/app/templates/Template_EquiArena.xlsx
+++ b/app/templates/Template_EquiArena.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EB3B573-F021-44BF-BD2F-C6517C65CDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16039C29-0C4A-4E1C-8012-ED7D1F99C089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -891,7 +891,7 @@
     <numFmt numFmtId="178" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1154,19 +1154,6 @@
       <vertAlign val="subscript"/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1681,12 +1668,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="469">
+  <cellXfs count="465">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2751,9 +2738,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="43" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -2835,7 +2819,7 @@
     <xf numFmtId="174" fontId="24" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2849,6 +2833,114 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
@@ -2877,121 +2969,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3054,48 +3071,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5546,10 +5521,10 @@
       <c r="H2" s="274"/>
       <c r="I2" s="274"/>
       <c r="J2" s="275"/>
-      <c r="M2" s="351" t="s">
+      <c r="M2" s="350" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="352"/>
+      <c r="N2" s="351"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="272"/>
@@ -5562,10 +5537,10 @@
       <c r="H3" s="274"/>
       <c r="I3" s="274"/>
       <c r="J3" s="275"/>
-      <c r="M3" s="351" t="s">
+      <c r="M3" s="350" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="353"/>
+      <c r="N3" s="352"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="272"/>
@@ -5578,10 +5553,10 @@
       <c r="H4" s="274"/>
       <c r="I4" s="274"/>
       <c r="J4" s="275"/>
-      <c r="M4" s="351" t="s">
+      <c r="M4" s="350" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="353"/>
+      <c r="N4" s="352"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="276"/>
@@ -5594,10 +5569,10 @@
       <c r="H5" s="277"/>
       <c r="I5" s="277"/>
       <c r="J5" s="278"/>
-      <c r="M5" s="351" t="s">
+      <c r="M5" s="350" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="353"/>
+      <c r="N5" s="352"/>
     </row>
     <row r="6" spans="1:14" ht="5.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="279"/>
@@ -5610,44 +5585,44 @@
       <c r="H6" s="279"/>
       <c r="I6" s="279"/>
       <c r="J6" s="279"/>
-      <c r="M6" s="354"/>
-      <c r="N6" s="355"/>
+      <c r="M6" s="353"/>
+      <c r="N6" s="354"/>
     </row>
     <row r="7" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="398" t="s">
+      <c r="A7" s="369" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="398"/>
-      <c r="C7" s="398"/>
-      <c r="D7" s="398"/>
-      <c r="E7" s="398"/>
-      <c r="F7" s="398"/>
-      <c r="G7" s="398"/>
-      <c r="H7" s="398"/>
-      <c r="I7" s="398"/>
-      <c r="J7" s="398"/>
-      <c r="M7" s="351" t="s">
+      <c r="B7" s="369"/>
+      <c r="C7" s="369"/>
+      <c r="D7" s="369"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
+      <c r="G7" s="369"/>
+      <c r="H7" s="369"/>
+      <c r="I7" s="369"/>
+      <c r="J7" s="369"/>
+      <c r="M7" s="350" t="s">
         <v>124</v>
       </c>
-      <c r="N7" s="355"/>
+      <c r="N7" s="354"/>
     </row>
     <row r="8" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="399" t="s">
+      <c r="A8" s="370" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="399"/>
-      <c r="C8" s="399"/>
-      <c r="D8" s="399"/>
-      <c r="E8" s="399"/>
-      <c r="F8" s="399"/>
-      <c r="G8" s="399"/>
-      <c r="H8" s="399"/>
-      <c r="I8" s="399"/>
-      <c r="J8" s="399"/>
-      <c r="M8" s="351" t="s">
+      <c r="B8" s="370"/>
+      <c r="C8" s="370"/>
+      <c r="D8" s="370"/>
+      <c r="E8" s="370"/>
+      <c r="F8" s="370"/>
+      <c r="G8" s="370"/>
+      <c r="H8" s="370"/>
+      <c r="I8" s="370"/>
+      <c r="J8" s="370"/>
+      <c r="M8" s="350" t="s">
         <v>172</v>
       </c>
-      <c r="N8" s="356"/>
+      <c r="N8" s="355"/>
     </row>
     <row r="9" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="280"/>
@@ -5660,51 +5635,51 @@
       <c r="H9" s="280"/>
       <c r="I9" s="280"/>
       <c r="J9" s="280"/>
-      <c r="M9" s="351" t="s">
+      <c r="M9" s="350" t="s">
         <v>173</v>
       </c>
-      <c r="N9" s="355"/>
+      <c r="N9" s="354"/>
     </row>
     <row r="10" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="400" t="s">
+      <c r="B10" s="371" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="400"/>
-      <c r="D10" s="400" t="s">
+      <c r="C10" s="371"/>
+      <c r="D10" s="371" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="400"/>
-      <c r="F10" s="400" t="s">
+      <c r="E10" s="371"/>
+      <c r="F10" s="371" t="s">
         <v>132</v>
       </c>
-      <c r="G10" s="400"/>
-      <c r="H10" s="400" t="s">
+      <c r="G10" s="371"/>
+      <c r="H10" s="371" t="s">
         <v>133</v>
       </c>
-      <c r="I10" s="400"/>
+      <c r="I10" s="371"/>
       <c r="J10" s="281"/>
       <c r="K10" s="282"/>
       <c r="L10" s="282"/>
-      <c r="M10" s="354"/>
-      <c r="N10" s="355"/>
+      <c r="M10" s="353"/>
+      <c r="N10" s="354"/>
     </row>
     <row r="11" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="283"/>
-      <c r="B11" s="400"/>
-      <c r="C11" s="400"/>
-      <c r="D11" s="400"/>
-      <c r="E11" s="400"/>
-      <c r="F11" s="400"/>
-      <c r="G11" s="400"/>
-      <c r="H11" s="400"/>
-      <c r="I11" s="400"/>
+      <c r="B11" s="371"/>
+      <c r="C11" s="371"/>
+      <c r="D11" s="371"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
+      <c r="G11" s="371"/>
+      <c r="H11" s="371"/>
+      <c r="I11" s="371"/>
       <c r="J11" s="284"/>
       <c r="K11" s="282"/>
       <c r="L11" s="282"/>
-      <c r="M11" s="351" t="s">
+      <c r="M11" s="350" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="355"/>
+      <c r="N11" s="354"/>
     </row>
     <row r="12" spans="1:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="283"/>
@@ -5719,48 +5694,48 @@
       <c r="J12" s="287"/>
       <c r="K12" s="282"/>
       <c r="L12" s="282"/>
-      <c r="M12" s="351" t="s">
+      <c r="M12" s="350" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="356"/>
+      <c r="N12" s="355"/>
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="401" t="s">
+      <c r="A13" s="372" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="402"/>
-      <c r="C13" s="402"/>
-      <c r="D13" s="402"/>
-      <c r="E13" s="402"/>
-      <c r="F13" s="402"/>
-      <c r="G13" s="402"/>
-      <c r="H13" s="402"/>
-      <c r="I13" s="402"/>
-      <c r="J13" s="403"/>
+      <c r="B13" s="373"/>
+      <c r="C13" s="373"/>
+      <c r="D13" s="373"/>
+      <c r="E13" s="373"/>
+      <c r="F13" s="373"/>
+      <c r="G13" s="373"/>
+      <c r="H13" s="373"/>
+      <c r="I13" s="373"/>
+      <c r="J13" s="374"/>
       <c r="K13" s="282"/>
       <c r="L13" s="282"/>
-      <c r="M13" s="351" t="s">
+      <c r="M13" s="350" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="356"/>
+      <c r="N13" s="355"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="395" t="s">
+      <c r="A14" s="366" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="396"/>
-      <c r="C14" s="396"/>
-      <c r="D14" s="396"/>
-      <c r="E14" s="396"/>
-      <c r="F14" s="396"/>
-      <c r="G14" s="396"/>
-      <c r="H14" s="396"/>
-      <c r="I14" s="396"/>
-      <c r="J14" s="397"/>
+      <c r="B14" s="367"/>
+      <c r="C14" s="367"/>
+      <c r="D14" s="367"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
+      <c r="G14" s="367"/>
+      <c r="H14" s="367"/>
+      <c r="I14" s="367"/>
+      <c r="J14" s="368"/>
       <c r="K14" s="282"/>
       <c r="L14" s="282"/>
-      <c r="M14" s="354"/>
-      <c r="N14" s="355"/>
+      <c r="M14" s="353"/>
+      <c r="N14" s="354"/>
     </row>
     <row r="15" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="288"/>
@@ -5775,60 +5750,60 @@
       <c r="J15" s="292"/>
       <c r="K15" s="282"/>
       <c r="L15" s="282"/>
-      <c r="M15" s="351" t="s">
+      <c r="M15" s="350" t="s">
         <v>174</v>
       </c>
-      <c r="N15" s="357"/>
+      <c r="N15" s="356"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="293"/>
-      <c r="B16" s="387" t="s">
+      <c r="B16" s="375" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="387"/>
-      <c r="D16" s="387"/>
+      <c r="C16" s="375"/>
+      <c r="D16" s="375"/>
       <c r="E16" s="294"/>
-      <c r="F16" s="388" t="s">
+      <c r="F16" s="376" t="s">
         <v>134</v>
       </c>
-      <c r="G16" s="388"/>
+      <c r="G16" s="376"/>
       <c r="H16" s="294"/>
-      <c r="I16" s="389" t="s">
+      <c r="I16" s="377" t="s">
         <v>135</v>
       </c>
-      <c r="J16" s="392"/>
+      <c r="J16" s="380"/>
       <c r="K16" s="282"/>
       <c r="L16" s="282"/>
-      <c r="M16" s="351" t="s">
+      <c r="M16" s="350" t="s">
         <v>27</v>
       </c>
-      <c r="N16" s="357"/>
+      <c r="N16" s="356"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="293"/>
-      <c r="B17" s="378"/>
-      <c r="C17" s="379"/>
-      <c r="D17" s="380"/>
+      <c r="B17" s="383"/>
+      <c r="C17" s="384"/>
+      <c r="D17" s="385"/>
       <c r="E17" s="295"/>
-      <c r="F17" s="378"/>
-      <c r="G17" s="380"/>
+      <c r="F17" s="383"/>
+      <c r="G17" s="385"/>
       <c r="H17" s="294"/>
-      <c r="I17" s="390"/>
-      <c r="J17" s="393"/>
+      <c r="I17" s="378"/>
+      <c r="J17" s="381"/>
       <c r="K17" s="282"/>
       <c r="L17" s="282"/>
-      <c r="M17" s="351" t="s">
+      <c r="M17" s="350" t="s">
         <v>175</v>
       </c>
-      <c r="N17" s="358"/>
+      <c r="N17" s="357"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E18" s="295"/>
       <c r="F18" s="295"/>
       <c r="G18" s="295"/>
       <c r="H18" s="294"/>
-      <c r="I18" s="391"/>
-      <c r="J18" s="394"/>
+      <c r="I18" s="379"/>
+      <c r="J18" s="382"/>
       <c r="L18" s="282"/>
       <c r="M18" s="296"/>
     </row>
@@ -5848,11 +5823,11 @@
     </row>
     <row r="20" spans="1:14" s="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="299"/>
-      <c r="B20" s="374" t="s">
+      <c r="B20" s="386" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="374"/>
-      <c r="D20" s="376"/>
+      <c r="C20" s="386"/>
+      <c r="D20" s="388"/>
       <c r="F20" s="301" t="s">
         <v>137</v>
       </c>
@@ -5865,12 +5840,12 @@
     </row>
     <row r="21" spans="1:14" s="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="304"/>
-      <c r="B21" s="375"/>
-      <c r="C21" s="375"/>
-      <c r="D21" s="377"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="379"/>
-      <c r="H21" s="380"/>
+      <c r="B21" s="387"/>
+      <c r="C21" s="387"/>
+      <c r="D21" s="389"/>
+      <c r="F21" s="383"/>
+      <c r="G21" s="384"/>
+      <c r="H21" s="385"/>
       <c r="I21" s="302"/>
       <c r="J21" s="298"/>
       <c r="L21" s="303"/>
@@ -6124,9 +6099,9 @@
       <c r="G35" s="322" t="s">
         <v>1</v>
       </c>
-      <c r="H35" s="337"/>
-      <c r="I35" s="337"/>
-      <c r="J35" s="337"/>
+      <c r="H35" s="208"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="208"/>
       <c r="K35" s="282"/>
       <c r="L35" s="282"/>
     </row>
@@ -6134,7 +6109,7 @@
       <c r="A36" s="318" t="s">
         <v>152</v>
       </c>
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="337" t="s">
         <v>71</v>
       </c>
       <c r="C36" s="320"/>
@@ -6144,58 +6119,56 @@
       <c r="G36" s="322" t="s">
         <v>1</v>
       </c>
-      <c r="H36" s="381">
-        <v>31</v>
-      </c>
-      <c r="I36" s="382"/>
-      <c r="J36" s="383"/>
+      <c r="H36" s="425"/>
+      <c r="I36" s="426"/>
+      <c r="J36" s="427"/>
       <c r="K36" s="282"/>
       <c r="L36" s="282"/>
     </row>
     <row r="37" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="339"/>
-      <c r="B37" s="339"/>
-      <c r="C37" s="340"/>
-      <c r="D37" s="341"/>
-      <c r="E37" s="341"/>
-      <c r="F37" s="341"/>
-      <c r="G37" s="341"/>
-      <c r="H37" s="341"/>
-      <c r="I37" s="341"/>
-      <c r="J37" s="342"/>
+      <c r="A37" s="338"/>
+      <c r="B37" s="338"/>
+      <c r="C37" s="339"/>
+      <c r="D37" s="340"/>
+      <c r="E37" s="340"/>
+      <c r="F37" s="340"/>
+      <c r="G37" s="340"/>
+      <c r="H37" s="340"/>
+      <c r="I37" s="340"/>
+      <c r="J37" s="341"/>
       <c r="K37" s="282"/>
       <c r="L37" s="282"/>
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="384" t="s">
+      <c r="A38" s="390" t="s">
         <v>153</v>
       </c>
-      <c r="B38" s="385"/>
-      <c r="C38" s="386"/>
-      <c r="D38" s="384" t="s">
+      <c r="B38" s="391"/>
+      <c r="C38" s="392"/>
+      <c r="D38" s="390" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="386"/>
-      <c r="F38" s="343" t="s">
+      <c r="E38" s="392"/>
+      <c r="F38" s="342" t="s">
         <v>104</v>
       </c>
-      <c r="G38" s="344"/>
-      <c r="H38" s="344"/>
-      <c r="I38" s="344"/>
-      <c r="J38" s="345"/>
+      <c r="G38" s="343"/>
+      <c r="H38" s="343"/>
+      <c r="I38" s="343"/>
+      <c r="J38" s="344"/>
       <c r="K38" s="282"/>
       <c r="L38" s="282"/>
     </row>
     <row r="39" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="367" t="s">
+      <c r="A39" s="393" t="s">
         <v>155</v>
       </c>
-      <c r="B39" s="368"/>
-      <c r="C39" s="369"/>
-      <c r="D39" s="367" t="s">
+      <c r="B39" s="394"/>
+      <c r="C39" s="395"/>
+      <c r="D39" s="393" t="s">
         <v>156</v>
       </c>
-      <c r="E39" s="369"/>
+      <c r="E39" s="395"/>
       <c r="F39" s="305"/>
       <c r="G39" s="306"/>
       <c r="H39" s="306"/>
@@ -6205,193 +6178,193 @@
       <c r="L39" s="282"/>
     </row>
     <row r="40" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="367" t="s">
+      <c r="A40" s="393" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="368"/>
-      <c r="C40" s="369"/>
-      <c r="D40" s="367" t="s">
+      <c r="B40" s="394"/>
+      <c r="C40" s="395"/>
+      <c r="D40" s="393" t="s">
         <v>158</v>
       </c>
-      <c r="E40" s="369"/>
-      <c r="F40" s="346"/>
-      <c r="G40" s="344"/>
-      <c r="H40" s="344"/>
-      <c r="I40" s="344"/>
-      <c r="J40" s="344"/>
+      <c r="E40" s="395"/>
+      <c r="F40" s="345"/>
+      <c r="G40" s="343"/>
+      <c r="H40" s="343"/>
+      <c r="I40" s="343"/>
+      <c r="J40" s="343"/>
       <c r="K40" s="282"/>
       <c r="L40" s="282"/>
     </row>
     <row r="41" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="367" t="s">
+      <c r="A41" s="393" t="s">
         <v>159</v>
       </c>
-      <c r="B41" s="368"/>
-      <c r="C41" s="369"/>
-      <c r="D41" s="367" t="s">
+      <c r="B41" s="394"/>
+      <c r="C41" s="395"/>
+      <c r="D41" s="393" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="369"/>
+      <c r="E41" s="395"/>
       <c r="F41" s="293"/>
       <c r="K41" s="282"/>
       <c r="L41" s="282"/>
     </row>
     <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="371" t="s">
+      <c r="A42" s="397" t="s">
         <v>161</v>
       </c>
-      <c r="B42" s="372"/>
-      <c r="C42" s="373"/>
-      <c r="D42" s="367" t="s">
+      <c r="B42" s="398"/>
+      <c r="C42" s="399"/>
+      <c r="D42" s="393" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="369"/>
+      <c r="E42" s="395"/>
       <c r="F42" s="293"/>
       <c r="K42" s="282"/>
       <c r="L42" s="282"/>
     </row>
     <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="371" t="s">
+      <c r="A43" s="397" t="s">
         <v>163</v>
       </c>
-      <c r="B43" s="372"/>
-      <c r="C43" s="373"/>
-      <c r="D43" s="367" t="s">
+      <c r="B43" s="398"/>
+      <c r="C43" s="399"/>
+      <c r="D43" s="393" t="s">
         <v>164</v>
       </c>
-      <c r="E43" s="369"/>
+      <c r="E43" s="395"/>
       <c r="F43" s="293"/>
       <c r="K43" s="282"/>
       <c r="L43" s="282"/>
     </row>
     <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="367" t="s">
+      <c r="A44" s="393" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="368"/>
-      <c r="C44" s="369"/>
-      <c r="D44" s="367" t="s">
+      <c r="B44" s="394"/>
+      <c r="C44" s="395"/>
+      <c r="D44" s="393" t="s">
         <v>166</v>
       </c>
-      <c r="E44" s="369"/>
+      <c r="E44" s="395"/>
       <c r="F44" s="293"/>
       <c r="K44" s="282"/>
       <c r="L44" s="282"/>
     </row>
     <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="367" t="s">
+      <c r="A45" s="393" t="s">
         <v>167</v>
       </c>
-      <c r="B45" s="368"/>
-      <c r="C45" s="369"/>
-      <c r="D45" s="367" t="s">
+      <c r="B45" s="394"/>
+      <c r="C45" s="395"/>
+      <c r="D45" s="393" t="s">
         <v>168</v>
       </c>
-      <c r="E45" s="369"/>
+      <c r="E45" s="395"/>
       <c r="F45" s="293"/>
       <c r="K45" s="282"/>
       <c r="L45" s="282"/>
     </row>
     <row r="46" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="347"/>
-      <c r="B46" s="347"/>
-      <c r="C46" s="342"/>
-      <c r="D46" s="342"/>
-      <c r="E46" s="342"/>
-      <c r="F46" s="342"/>
-      <c r="G46" s="342"/>
-      <c r="H46" s="342"/>
-      <c r="I46" s="342"/>
-      <c r="J46" s="342"/>
+      <c r="A46" s="346"/>
+      <c r="B46" s="346"/>
+      <c r="C46" s="341"/>
+      <c r="D46" s="341"/>
+      <c r="E46" s="341"/>
+      <c r="F46" s="341"/>
+      <c r="G46" s="341"/>
+      <c r="H46" s="341"/>
+      <c r="I46" s="341"/>
+      <c r="J46" s="341"/>
       <c r="K46" s="282"/>
       <c r="L46" s="282"/>
     </row>
     <row r="47" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="348"/>
-      <c r="B47" s="348"/>
-      <c r="C47" s="342"/>
-      <c r="J47" s="342"/>
+      <c r="A47" s="347"/>
+      <c r="B47" s="347"/>
+      <c r="C47" s="341"/>
+      <c r="J47" s="341"/>
       <c r="K47" s="282"/>
       <c r="L47" s="282"/>
     </row>
     <row r="48" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="348"/>
-      <c r="B48" s="348"/>
-      <c r="C48" s="342"/>
-      <c r="J48" s="342"/>
+      <c r="A48" s="347"/>
+      <c r="B48" s="347"/>
+      <c r="C48" s="341"/>
+      <c r="J48" s="341"/>
       <c r="K48" s="282"/>
       <c r="L48" s="282"/>
     </row>
     <row r="49" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="348"/>
-      <c r="B49" s="348"/>
-      <c r="C49" s="342"/>
-      <c r="J49" s="342"/>
+      <c r="A49" s="347"/>
+      <c r="B49" s="347"/>
+      <c r="C49" s="341"/>
+      <c r="J49" s="341"/>
       <c r="K49" s="282"/>
       <c r="L49" s="282"/>
     </row>
     <row r="50" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="349"/>
-      <c r="B50" s="349"/>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
-      <c r="G50" s="342"/>
-      <c r="H50" s="342"/>
-      <c r="I50" s="342"/>
-      <c r="J50" s="342"/>
+      <c r="A50" s="348"/>
+      <c r="B50" s="348"/>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
+      <c r="G50" s="341"/>
+      <c r="H50" s="341"/>
+      <c r="I50" s="341"/>
+      <c r="J50" s="341"/>
       <c r="K50" s="282"/>
       <c r="L50" s="282"/>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="350" t="s">
+      <c r="A51" s="349" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="350"/>
-      <c r="C51" s="342"/>
-      <c r="D51" s="342"/>
-      <c r="E51" s="342"/>
-      <c r="F51" s="342"/>
-      <c r="G51" s="342"/>
-      <c r="H51" s="342"/>
-      <c r="I51" s="342"/>
-      <c r="J51" s="342"/>
+      <c r="B51" s="349"/>
+      <c r="C51" s="341"/>
+      <c r="D51" s="341"/>
+      <c r="E51" s="341"/>
+      <c r="F51" s="341"/>
+      <c r="G51" s="341"/>
+      <c r="H51" s="341"/>
+      <c r="I51" s="341"/>
+      <c r="J51" s="341"/>
       <c r="K51" s="282"/>
       <c r="L51" s="282"/>
     </row>
     <row r="52" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="350" t="s">
+      <c r="A52" s="349" t="s">
         <v>169</v>
       </c>
-      <c r="B52" s="350"/>
-      <c r="C52" s="342"/>
-      <c r="D52" s="342"/>
-      <c r="E52" s="342"/>
+      <c r="B52" s="349"/>
+      <c r="C52" s="341"/>
+      <c r="D52" s="341"/>
+      <c r="E52" s="341"/>
       <c r="F52" s="327" t="s">
         <v>170</v>
       </c>
-      <c r="G52" s="342"/>
-      <c r="H52" s="342"/>
-      <c r="I52" s="342"/>
-      <c r="J52" s="342"/>
+      <c r="G52" s="341"/>
+      <c r="H52" s="341"/>
+      <c r="I52" s="341"/>
+      <c r="J52" s="341"/>
       <c r="K52" s="282"/>
       <c r="L52" s="282"/>
     </row>
     <row r="53" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="370" t="s">
+      <c r="A54" s="396" t="s">
         <v>171</v>
       </c>
-      <c r="B54" s="370"/>
-      <c r="C54" s="370"/>
-      <c r="D54" s="370"/>
-      <c r="E54" s="370"/>
-      <c r="F54" s="370"/>
-      <c r="G54" s="370"/>
-      <c r="H54" s="370"/>
-      <c r="I54" s="370"/>
-      <c r="J54" s="370"/>
+      <c r="B54" s="396"/>
+      <c r="C54" s="396"/>
+      <c r="D54" s="396"/>
+      <c r="E54" s="396"/>
+      <c r="F54" s="396"/>
+      <c r="G54" s="396"/>
+      <c r="H54" s="396"/>
+      <c r="I54" s="396"/>
+      <c r="J54" s="396"/>
     </row>
     <row r="55" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6403,6 +6376,33 @@
     <protectedRange sqref="H31:J31" name="Rango8_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:G17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A8:J8"/>
@@ -6415,33 +6415,6 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:E44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.39370078740157483" top="0" bottom="0" header="0" footer="0"/>
@@ -6492,38 +6465,38 @@
       <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="423" t="s">
+      <c r="A2" s="400" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="423"/>
-      <c r="C2" s="423"/>
-      <c r="D2" s="423"/>
-      <c r="E2" s="423"/>
-      <c r="F2" s="423"/>
-      <c r="G2" s="423"/>
-      <c r="H2" s="423"/>
-      <c r="I2" s="423"/>
-      <c r="J2" s="423"/>
-      <c r="K2" s="423"/>
-      <c r="L2" s="423"/>
-      <c r="M2" s="423"/>
+      <c r="B2" s="400"/>
+      <c r="C2" s="400"/>
+      <c r="D2" s="400"/>
+      <c r="E2" s="400"/>
+      <c r="F2" s="400"/>
+      <c r="G2" s="400"/>
+      <c r="H2" s="400"/>
+      <c r="I2" s="400"/>
+      <c r="J2" s="400"/>
+      <c r="K2" s="400"/>
+      <c r="L2" s="400"/>
+      <c r="M2" s="400"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="424">
+      <c r="A3" s="401">
         <v>0</v>
       </c>
-      <c r="B3" s="424"/>
-      <c r="C3" s="424"/>
-      <c r="D3" s="424"/>
-      <c r="E3" s="424"/>
-      <c r="F3" s="424"/>
-      <c r="G3" s="424"/>
-      <c r="H3" s="424"/>
-      <c r="I3" s="424"/>
-      <c r="J3" s="424"/>
-      <c r="K3" s="424"/>
-      <c r="L3" s="424"/>
-      <c r="M3" s="424"/>
+      <c r="B3" s="401"/>
+      <c r="C3" s="401"/>
+      <c r="D3" s="401"/>
+      <c r="E3" s="401"/>
+      <c r="F3" s="401"/>
+      <c r="G3" s="401"/>
+      <c r="H3" s="401"/>
+      <c r="I3" s="401"/>
+      <c r="J3" s="401"/>
+      <c r="K3" s="401"/>
+      <c r="L3" s="401"/>
+      <c r="M3" s="401"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6533,17 +6506,17 @@
       <c r="B5" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="435">
+      <c r="C5" s="412">
         <f>+FORMATO!N2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="435"/>
-      <c r="E5" s="435"/>
-      <c r="F5" s="435"/>
-      <c r="G5" s="435"/>
-      <c r="H5" s="435"/>
-      <c r="I5" s="435"/>
-      <c r="J5" s="435"/>
+      <c r="D5" s="412"/>
+      <c r="E5" s="412"/>
+      <c r="F5" s="412"/>
+      <c r="G5" s="412"/>
+      <c r="H5" s="412"/>
+      <c r="I5" s="412"/>
+      <c r="J5" s="412"/>
       <c r="K5" s="55" t="s">
         <v>20</v>
       </c>
@@ -6561,17 +6534,17 @@
       <c r="B6" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="435">
+      <c r="C6" s="412">
         <f>+FORMATO!N3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="435"/>
-      <c r="E6" s="435"/>
-      <c r="F6" s="435"/>
-      <c r="G6" s="435"/>
-      <c r="H6" s="435"/>
-      <c r="I6" s="435"/>
-      <c r="J6" s="435"/>
+      <c r="D6" s="412"/>
+      <c r="E6" s="412"/>
+      <c r="F6" s="412"/>
+      <c r="G6" s="412"/>
+      <c r="H6" s="412"/>
+      <c r="I6" s="412"/>
+      <c r="J6" s="412"/>
       <c r="K6" s="57" t="s">
         <v>124</v>
       </c>
@@ -6593,18 +6566,18 @@
       <c r="B7" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="435">
+      <c r="C7" s="412">
         <f>+FORMATO!N4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="435"/>
-      <c r="E7" s="435"/>
-      <c r="F7" s="435"/>
-      <c r="G7" s="435"/>
-      <c r="H7" s="435"/>
-      <c r="I7" s="435"/>
-      <c r="J7" s="435"/>
-      <c r="K7" s="366" t="s">
+      <c r="D7" s="412"/>
+      <c r="E7" s="412"/>
+      <c r="F7" s="412"/>
+      <c r="G7" s="412"/>
+      <c r="H7" s="412"/>
+      <c r="I7" s="412"/>
+      <c r="J7" s="412"/>
+      <c r="K7" s="365" t="s">
         <v>36</v>
       </c>
       <c r="L7" s="54" t="s">
@@ -6625,18 +6598,18 @@
       <c r="B8" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="435">
+      <c r="C8" s="412">
         <f>+FORMATO!N5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="435"/>
-      <c r="E8" s="435"/>
-      <c r="F8" s="435"/>
-      <c r="G8" s="435"/>
-      <c r="H8" s="435"/>
-      <c r="I8" s="435"/>
-      <c r="J8" s="435"/>
-      <c r="K8" s="435"/>
+      <c r="D8" s="412"/>
+      <c r="E8" s="412"/>
+      <c r="F8" s="412"/>
+      <c r="G8" s="412"/>
+      <c r="H8" s="412"/>
+      <c r="I8" s="412"/>
+      <c r="J8" s="412"/>
+      <c r="K8" s="412"/>
       <c r="L8" s="54"/>
       <c r="M8" s="31"/>
       <c r="N8" s="30"/>
@@ -6664,41 +6637,41 @@
       <c r="P9" s="30"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="427" t="s">
+      <c r="A10" s="404" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="428"/>
-      <c r="C10" s="428"/>
-      <c r="D10" s="428"/>
-      <c r="E10" s="428"/>
-      <c r="F10" s="428"/>
-      <c r="G10" s="428"/>
-      <c r="H10" s="428"/>
-      <c r="I10" s="428"/>
-      <c r="J10" s="428"/>
-      <c r="K10" s="428"/>
-      <c r="L10" s="428"/>
-      <c r="M10" s="429"/>
+      <c r="B10" s="405"/>
+      <c r="C10" s="405"/>
+      <c r="D10" s="405"/>
+      <c r="E10" s="405"/>
+      <c r="F10" s="405"/>
+      <c r="G10" s="405"/>
+      <c r="H10" s="405"/>
+      <c r="I10" s="405"/>
+      <c r="J10" s="405"/>
+      <c r="K10" s="405"/>
+      <c r="L10" s="405"/>
+      <c r="M10" s="406"/>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
       <c r="P10" s="30"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="430" t="s">
+      <c r="A11" s="407" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="431"/>
-      <c r="C11" s="431"/>
-      <c r="D11" s="431"/>
-      <c r="E11" s="431"/>
-      <c r="F11" s="431"/>
-      <c r="G11" s="431"/>
-      <c r="H11" s="431"/>
-      <c r="I11" s="431"/>
-      <c r="J11" s="431"/>
-      <c r="K11" s="431"/>
-      <c r="L11" s="431"/>
-      <c r="M11" s="432"/>
+      <c r="B11" s="408"/>
+      <c r="C11" s="408"/>
+      <c r="D11" s="408"/>
+      <c r="E11" s="408"/>
+      <c r="F11" s="408"/>
+      <c r="G11" s="408"/>
+      <c r="H11" s="408"/>
+      <c r="I11" s="408"/>
+      <c r="J11" s="408"/>
+      <c r="K11" s="408"/>
+      <c r="L11" s="408"/>
+      <c r="M11" s="409"/>
       <c r="N11" s="30"/>
       <c r="O11" s="30"/>
       <c r="P11" s="30"/>
@@ -6722,13 +6695,13 @@
       <c r="P12" s="30"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="433" t="s">
+      <c r="A13" s="410" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="434"/>
-      <c r="C13" s="434"/>
-      <c r="D13" s="434"/>
-      <c r="E13" s="434"/>
+      <c r="B13" s="411"/>
+      <c r="C13" s="411"/>
+      <c r="D13" s="411"/>
+      <c r="E13" s="411"/>
       <c r="F13" s="245"/>
       <c r="G13" s="245"/>
       <c r="H13" s="245"/>
@@ -6749,7 +6722,7 @@
       <c r="D14" s="248" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="365">
+      <c r="E14" s="364">
         <f>+FORMATO!N15</f>
         <v>0</v>
       </c>
@@ -6779,7 +6752,7 @@
       <c r="D15" s="248" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="365">
+      <c r="E15" s="364">
         <f>+FORMATO!N16</f>
         <v>0</v>
       </c>
@@ -6810,7 +6783,7 @@
       <c r="D16" s="248" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="365">
+      <c r="E16" s="364">
         <f>+FORMATO!N17</f>
         <v>0</v>
       </c>
@@ -6859,15 +6832,15 @@
       <c r="A18" s="65"/>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
-      <c r="D18" s="425"/>
-      <c r="E18" s="425"/>
+      <c r="D18" s="402"/>
+      <c r="E18" s="402"/>
       <c r="F18" s="66"/>
       <c r="G18" s="66"/>
       <c r="H18" s="66"/>
       <c r="I18" s="43"/>
       <c r="J18" s="43"/>
-      <c r="K18" s="426"/>
-      <c r="L18" s="426"/>
+      <c r="K18" s="403"/>
+      <c r="L18" s="403"/>
       <c r="M18" s="77"/>
       <c r="N18" s="30"/>
       <c r="O18" s="44"/>
@@ -6877,18 +6850,18 @@
       <c r="A19" s="99"/>
       <c r="B19" s="100"/>
       <c r="C19" s="100"/>
-      <c r="D19" s="404" t="s">
+      <c r="D19" s="413" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="405"/>
-      <c r="F19" s="405"/>
-      <c r="G19" s="405"/>
-      <c r="H19" s="406"/>
-      <c r="I19" s="421" t="s">
+      <c r="E19" s="414"/>
+      <c r="F19" s="414"/>
+      <c r="G19" s="414"/>
+      <c r="H19" s="415"/>
+      <c r="I19" s="430" t="s">
         <v>74</v>
       </c>
-      <c r="J19" s="421"/>
-      <c r="K19" s="422"/>
+      <c r="J19" s="430"/>
+      <c r="K19" s="431"/>
       <c r="L19" s="101"/>
       <c r="M19" s="102"/>
       <c r="N19" s="30"/>
@@ -6899,11 +6872,11 @@
       <c r="A20" s="67"/>
       <c r="B20" s="52"/>
       <c r="C20" s="52"/>
-      <c r="D20" s="407"/>
-      <c r="E20" s="408"/>
-      <c r="F20" s="408"/>
-      <c r="G20" s="408"/>
-      <c r="H20" s="409"/>
+      <c r="D20" s="416"/>
+      <c r="E20" s="417"/>
+      <c r="F20" s="417"/>
+      <c r="G20" s="417"/>
+      <c r="H20" s="418"/>
       <c r="I20" s="113">
         <v>1</v>
       </c>
@@ -6975,8 +6948,8 @@
         <f>+Datos!I14</f>
         <v>0</v>
       </c>
-      <c r="L22" s="415"/>
-      <c r="M22" s="414"/>
+      <c r="L22" s="424"/>
+      <c r="M22" s="423"/>
       <c r="N22" s="30"/>
       <c r="O22" s="47"/>
       <c r="P22" s="30"/>
@@ -7006,8 +6979,8 @@
         <f>+Datos!I15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L23" s="413"/>
-      <c r="M23" s="414"/>
+      <c r="L23" s="422"/>
+      <c r="M23" s="423"/>
       <c r="N23" s="30"/>
       <c r="O23" s="30"/>
       <c r="P23" s="47"/>
@@ -7025,12 +6998,12 @@
       <c r="H24" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="416" t="e">
+      <c r="I24" s="425" t="e">
         <f>+Datos!G16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J24" s="417"/>
-      <c r="K24" s="418"/>
+      <c r="J24" s="426"/>
+      <c r="K24" s="427"/>
       <c r="L24" s="81"/>
       <c r="M24" s="79"/>
       <c r="N24" s="30"/>
@@ -7092,10 +7065,10 @@
       <c r="C28" s="85"/>
       <c r="D28" s="84"/>
       <c r="E28" s="81"/>
-      <c r="F28" s="419" t="s">
+      <c r="F28" s="428" t="s">
         <v>126</v>
       </c>
-      <c r="G28" s="420"/>
+      <c r="G28" s="429"/>
       <c r="M28" s="109"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -7118,11 +7091,11 @@
       <c r="C30" s="85"/>
       <c r="D30" s="84"/>
       <c r="E30" s="81"/>
-      <c r="F30" s="410">
+      <c r="F30" s="419">
         <f>+Datos!E25</f>
         <v>0</v>
       </c>
-      <c r="G30" s="411"/>
+      <c r="G30" s="420"/>
       <c r="M30" s="109"/>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7133,11 +7106,11 @@
       <c r="C31" s="85"/>
       <c r="D31" s="84"/>
       <c r="E31" s="81"/>
-      <c r="F31" s="410">
+      <c r="F31" s="419">
         <f>+Datos!E26</f>
         <v>0</v>
       </c>
-      <c r="G31" s="411"/>
+      <c r="G31" s="420"/>
       <c r="M31" s="109"/>
     </row>
     <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7198,21 +7171,21 @@
       <c r="C36" s="95"/>
     </row>
     <row r="37" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="412" t="s">
+      <c r="A37" s="421" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="412"/>
-      <c r="C37" s="412"/>
-      <c r="D37" s="412"/>
-      <c r="E37" s="412"/>
-      <c r="F37" s="412"/>
-      <c r="G37" s="412"/>
-      <c r="H37" s="412"/>
-      <c r="I37" s="412"/>
-      <c r="J37" s="412"/>
-      <c r="K37" s="412"/>
-      <c r="L37" s="412"/>
-      <c r="M37" s="412"/>
+      <c r="B37" s="421"/>
+      <c r="C37" s="421"/>
+      <c r="D37" s="421"/>
+      <c r="E37" s="421"/>
+      <c r="F37" s="421"/>
+      <c r="G37" s="421"/>
+      <c r="H37" s="421"/>
+      <c r="I37" s="421"/>
+      <c r="J37" s="421"/>
+      <c r="K37" s="421"/>
+      <c r="L37" s="421"/>
+      <c r="M37" s="421"/>
       <c r="N37" s="30"/>
       <c r="O37" s="30"/>
       <c r="P37" s="30"/>
@@ -7228,21 +7201,21 @@
       <c r="P38" s="30"/>
     </row>
     <row r="39" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="412" t="s">
+      <c r="A39" s="421" t="s">
         <v>122</v>
       </c>
-      <c r="B39" s="412"/>
-      <c r="C39" s="412"/>
-      <c r="D39" s="412"/>
-      <c r="E39" s="412"/>
-      <c r="F39" s="412"/>
-      <c r="G39" s="412"/>
-      <c r="H39" s="412"/>
-      <c r="I39" s="412"/>
-      <c r="J39" s="412"/>
-      <c r="K39" s="412"/>
-      <c r="L39" s="412"/>
-      <c r="M39" s="412"/>
+      <c r="B39" s="421"/>
+      <c r="C39" s="421"/>
+      <c r="D39" s="421"/>
+      <c r="E39" s="421"/>
+      <c r="F39" s="421"/>
+      <c r="G39" s="421"/>
+      <c r="H39" s="421"/>
+      <c r="I39" s="421"/>
+      <c r="J39" s="421"/>
+      <c r="K39" s="421"/>
+      <c r="L39" s="421"/>
+      <c r="M39" s="421"/>
       <c r="N39" s="30"/>
       <c r="O39" s="30"/>
       <c r="P39" s="30"/>
@@ -7447,6 +7420,16 @@
     <protectedRange sqref="C5:E6" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="21">
+    <mergeCell ref="D19:H20"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="I19:K19"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="D18:E18"/>
@@ -7458,16 +7441,6 @@
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="C7:J7"/>
     <mergeCell ref="C8:K8"/>
-    <mergeCell ref="D19:H20"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="A39:M39"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="I19:K19"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28:G28" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -7502,19 +7475,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="427" t="s">
+      <c r="A1" s="404" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="428"/>
-      <c r="C1" s="428"/>
-      <c r="D1" s="428"/>
-      <c r="E1" s="428"/>
-      <c r="F1" s="428"/>
-      <c r="G1" s="428"/>
-      <c r="H1" s="428"/>
-      <c r="I1" s="428"/>
-      <c r="J1" s="428"/>
-      <c r="K1" s="429"/>
+      <c r="B1" s="405"/>
+      <c r="C1" s="405"/>
+      <c r="D1" s="405"/>
+      <c r="E1" s="405"/>
+      <c r="F1" s="405"/>
+      <c r="G1" s="405"/>
+      <c r="H1" s="405"/>
+      <c r="I1" s="405"/>
+      <c r="J1" s="405"/>
+      <c r="K1" s="406"/>
       <c r="L1" s="243" t="s">
         <v>120</v>
       </c>
@@ -7522,19 +7495,19 @@
       <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="430" t="s">
+      <c r="A2" s="407" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="431"/>
-      <c r="C2" s="431"/>
-      <c r="D2" s="431"/>
-      <c r="E2" s="431"/>
-      <c r="F2" s="431"/>
-      <c r="G2" s="431"/>
-      <c r="H2" s="431"/>
-      <c r="I2" s="431"/>
-      <c r="J2" s="431"/>
-      <c r="K2" s="432"/>
+      <c r="B2" s="408"/>
+      <c r="C2" s="408"/>
+      <c r="D2" s="408"/>
+      <c r="E2" s="408"/>
+      <c r="F2" s="408"/>
+      <c r="G2" s="408"/>
+      <c r="H2" s="408"/>
+      <c r="I2" s="408"/>
+      <c r="J2" s="408"/>
+      <c r="K2" s="409"/>
       <c r="L2" s="255"/>
       <c r="M2" s="30">
         <f>+FORMATO!H11</f>
@@ -7560,18 +7533,18 @@
     </row>
     <row r="4" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="99"/>
-      <c r="B4" s="404" t="s">
+      <c r="B4" s="413" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="405"/>
-      <c r="D4" s="405"/>
-      <c r="E4" s="405"/>
-      <c r="F4" s="406"/>
-      <c r="G4" s="421" t="s">
+      <c r="C4" s="414"/>
+      <c r="D4" s="414"/>
+      <c r="E4" s="414"/>
+      <c r="F4" s="415"/>
+      <c r="G4" s="430" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="421"/>
-      <c r="I4" s="422"/>
+      <c r="H4" s="430"/>
+      <c r="I4" s="431"/>
       <c r="J4" s="101"/>
       <c r="K4" s="102"/>
       <c r="L4" s="30"/>
@@ -7580,11 +7553,11 @@
     </row>
     <row r="5" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="67"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="408"/>
-      <c r="D5" s="408"/>
-      <c r="E5" s="408"/>
-      <c r="F5" s="409"/>
+      <c r="B5" s="416"/>
+      <c r="C5" s="417"/>
+      <c r="D5" s="417"/>
+      <c r="E5" s="417"/>
+      <c r="F5" s="418"/>
       <c r="G5" s="113">
         <v>1</v>
       </c>
@@ -7859,8 +7832,8 @@
         <f>+FORMATO!J34</f>
         <v>0</v>
       </c>
-      <c r="J14" s="415"/>
-      <c r="K14" s="414"/>
+      <c r="J14" s="424"/>
+      <c r="K14" s="423"/>
       <c r="M14" s="45"/>
       <c r="N14" s="46"/>
     </row>
@@ -7903,12 +7876,12 @@
       <c r="F16" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="416" t="e">
+      <c r="G16" s="425" t="e">
         <f>ROUNDUP((AVERAGE(G15:I15)),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="417"/>
-      <c r="I16" s="418"/>
+      <c r="H16" s="426"/>
+      <c r="I16" s="427"/>
       <c r="J16" s="81"/>
       <c r="K16" s="79"/>
       <c r="M16" s="45"/>
@@ -7934,13 +7907,13 @@
     <row r="18" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="129"/>
       <c r="C18" s="214"/>
-      <c r="D18" s="438" t="s">
+      <c r="D18" s="434" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="439"/>
-      <c r="F18" s="439"/>
-      <c r="G18" s="439"/>
-      <c r="H18" s="439"/>
+      <c r="E18" s="435"/>
+      <c r="F18" s="435"/>
+      <c r="G18" s="435"/>
+      <c r="H18" s="435"/>
       <c r="I18" s="127"/>
       <c r="J18" s="86"/>
       <c r="K18" s="130"/>
@@ -7951,15 +7924,15 @@
     <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="129"/>
       <c r="C19" s="52"/>
-      <c r="D19" s="436" t="s">
+      <c r="D19" s="432" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="437"/>
-      <c r="F19" s="436" t="s">
+      <c r="E19" s="433"/>
+      <c r="F19" s="432" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="437"/>
-      <c r="H19" s="440" t="s">
+      <c r="G19" s="433"/>
+      <c r="H19" s="436" t="s">
         <v>90</v>
       </c>
       <c r="I19" s="127"/>
@@ -7984,7 +7957,7 @@
       <c r="G20" s="215" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="441"/>
+      <c r="H20" s="437"/>
       <c r="I20" s="127"/>
       <c r="J20" s="86"/>
       <c r="K20" s="130"/>
@@ -8285,16 +8258,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="456"/>
-      <c r="B1" s="456"/>
-      <c r="C1" s="447" t="s">
+      <c r="A1" s="452"/>
+      <c r="B1" s="452"/>
+      <c r="C1" s="443" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
-      <c r="H1" s="449"/>
+      <c r="D1" s="444"/>
+      <c r="E1" s="444"/>
+      <c r="F1" s="444"/>
+      <c r="G1" s="444"/>
+      <c r="H1" s="445"/>
       <c r="I1" s="153" t="s">
         <v>56</v>
       </c>
@@ -8303,14 +8276,14 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="456"/>
-      <c r="B2" s="456"/>
-      <c r="C2" s="450"/>
-      <c r="D2" s="451"/>
-      <c r="E2" s="451"/>
-      <c r="F2" s="451"/>
-      <c r="G2" s="451"/>
-      <c r="H2" s="452"/>
+      <c r="A2" s="452"/>
+      <c r="B2" s="452"/>
+      <c r="C2" s="446"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
+      <c r="H2" s="448"/>
       <c r="I2" s="153" t="s">
         <v>54</v>
       </c>
@@ -8319,30 +8292,30 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="456"/>
-      <c r="B3" s="456"/>
-      <c r="C3" s="450"/>
-      <c r="D3" s="451"/>
-      <c r="E3" s="451"/>
-      <c r="F3" s="451"/>
-      <c r="G3" s="451"/>
-      <c r="H3" s="452"/>
+      <c r="A3" s="452"/>
+      <c r="B3" s="452"/>
+      <c r="C3" s="446"/>
+      <c r="D3" s="447"/>
+      <c r="E3" s="447"/>
+      <c r="F3" s="447"/>
+      <c r="G3" s="447"/>
+      <c r="H3" s="448"/>
       <c r="I3" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="361">
+      <c r="J3" s="360">
         <v>46146</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="456"/>
-      <c r="B4" s="456"/>
-      <c r="C4" s="453"/>
-      <c r="D4" s="454"/>
-      <c r="E4" s="454"/>
-      <c r="F4" s="454"/>
-      <c r="G4" s="454"/>
-      <c r="H4" s="455"/>
+      <c r="A4" s="452"/>
+      <c r="B4" s="452"/>
+      <c r="C4" s="449"/>
+      <c r="D4" s="450"/>
+      <c r="E4" s="450"/>
+      <c r="F4" s="450"/>
+      <c r="G4" s="450"/>
+      <c r="H4" s="451"/>
       <c r="I4" s="153" t="s">
         <v>52</v>
       </c>
@@ -9280,8 +9253,8 @@
       <c r="J45" s="155"/>
     </row>
     <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="445"/>
-      <c r="B46" s="446"/>
+      <c r="A46" s="441"/>
+      <c r="B46" s="442"/>
       <c r="C46" s="195" t="e">
         <f>SUM(C43:C45)</f>
         <v>#DIV/0!</v>
@@ -9307,22 +9280,22 @@
       <c r="J47" s="155"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="362" t="s">
+      <c r="A55" s="361" t="s">
         <v>177</v>
       </c>
-      <c r="B55" s="457" t="s">
+      <c r="B55" s="453" t="s">
         <v>178</v>
       </c>
-      <c r="C55" s="458"/>
-      <c r="D55" s="363"/>
-      <c r="E55" s="459" t="s">
+      <c r="C55" s="454"/>
+      <c r="D55" s="362"/>
+      <c r="E55" s="455" t="s">
         <v>179</v>
       </c>
-      <c r="F55" s="459"/>
-      <c r="G55" s="460" t="s">
+      <c r="F55" s="455"/>
+      <c r="G55" s="456" t="s">
         <v>180</v>
       </c>
-      <c r="H55" s="461"/>
+      <c r="H55" s="457"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="223"/>
@@ -9335,22 +9308,22 @@
       <c r="H56" s="223"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="359" t="s">
+      <c r="A57" s="358" t="s">
         <v>181</v>
       </c>
-      <c r="B57" s="442">
+      <c r="B57" s="438">
         <v>44869</v>
       </c>
-      <c r="C57" s="443"/>
+      <c r="C57" s="439"/>
       <c r="D57" s="223"/>
-      <c r="E57" s="444" t="s">
+      <c r="E57" s="440" t="s">
         <v>182</v>
       </c>
-      <c r="F57" s="444"/>
-      <c r="G57" s="442">
+      <c r="F57" s="440"/>
+      <c r="G57" s="438">
         <v>44870</v>
       </c>
-      <c r="H57" s="443"/>
+      <c r="H57" s="439"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="223"/>
@@ -9441,12 +9414,12 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="463" t="s">
+      <c r="A9" s="459" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="464"/>
-      <c r="C9" s="464"/>
-      <c r="D9" s="464"/>
+      <c r="B9" s="460"/>
+      <c r="C9" s="460"/>
+      <c r="D9" s="460"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
     </row>
@@ -9520,18 +9493,18 @@
       <c r="G16" s="139"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="465" t="s">
+      <c r="A17" s="461" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="465"/>
+      <c r="B17" s="461"/>
       <c r="C17" s="151">
         <f>COUNT(B13:C16)</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="465"/>
-      <c r="B18" s="465"/>
+      <c r="A18" s="461"/>
+      <c r="B18" s="461"/>
       <c r="C18" s="152">
         <f>STDEV(B13:C16)/SQRT($C$17)</f>
         <v>3.0731814857649951E-2</v>
@@ -9553,49 +9526,49 @@
       <c r="D20" s="21"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="444"/>
+      <c r="A21" s="440"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="444"/>
+      <c r="A22" s="440"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="444"/>
+      <c r="A23" s="440"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="444"/>
+      <c r="A24" s="440"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
       <c r="D24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="462"/>
+      <c r="A25" s="458"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
       <c r="D25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="462"/>
+      <c r="A26" s="458"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
       <c r="D26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="462"/>
+      <c r="A27" s="458"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="462"/>
+      <c r="A28" s="458"/>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
@@ -9638,16 +9611,16 @@
     </row>
     <row r="3" spans="1:11" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="364" t="s">
+      <c r="A4" s="363" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="137"/>
       <c r="H5" s="258"/>
-      <c r="I5" s="466"/>
-      <c r="J5" s="466"/>
-      <c r="K5" s="466"/>
+      <c r="I5" s="462"/>
+      <c r="J5" s="462"/>
+      <c r="K5" s="462"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="137" t="s">
@@ -9664,7 +9637,7 @@
     <row r="7" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="137"/>
       <c r="B7" s="262"/>
-      <c r="H7" s="360"/>
+      <c r="H7" s="359"/>
       <c r="I7" s="261"/>
       <c r="J7" s="261"/>
       <c r="K7" s="261"/>
@@ -9673,22 +9646,22 @@
       <c r="A8" s="263" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="467">
+      <c r="B8" s="463">
         <v>0.9775252199076786</v>
       </c>
-      <c r="C8" s="467"/>
-      <c r="D8" s="467"/>
+      <c r="C8" s="463"/>
+      <c r="D8" s="463"/>
       <c r="E8" s="136"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="263" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="467">
+      <c r="B9" s="463">
         <v>0.99721835344343934</v>
       </c>
-      <c r="C9" s="467"/>
-      <c r="D9" s="467"/>
+      <c r="C9" s="463"/>
+      <c r="D9" s="463"/>
       <c r="E9" s="136"/>
     </row>
   </sheetData>
@@ -9719,10 +9692,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="468" t="s">
+      <c r="A2" s="464" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="468"/>
+      <c r="B2" s="464"/>
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
